--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487928_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487928_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7361</v>
+        <v>3.1956</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9852</v>
+        <v>1.0923</v>
       </c>
       <c r="F2" t="n">
-        <v>1.751</v>
+        <v>2.1033</v>
       </c>
       <c r="G2" t="n">
         <v>0.2966</v>
@@ -610,13 +610,13 @@
         <v>2.0812</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3523</v>
+        <v>0.1072</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.199</v>
+        <v>-0.0919</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1533</v>
+        <v>0.199</v>
       </c>
       <c r="V2" t="n">
         <v>1.7513</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. SAGNIA</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8347</v>
+        <v>1.3576</v>
       </c>
       <c r="E3" t="n">
-        <v>1.818</v>
+        <v>-2.0243</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9833</v>
+        <v>3.382</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.6128</v>
+        <v>-0.6288</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6952</v>
+        <v>-1.5415</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9177</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.6168</v>
+        <v>-1.4696</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6952</v>
+        <v>-2.6272</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0784</v>
+        <v>1.1577</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.996</v>
+        <v>0.8408</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.0857</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.996</v>
+        <v>-0.2449</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6244</v>
+        <v>2.2893</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6244</v>
+        <v>2.2893</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1156</v>
+        <v>-0.3029</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0373</v>
+        <v>-0.5548</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.2519</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5612</v>
+        <v>0.9018</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.4987</v>
+        <v>-1.0701</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0599</v>
+        <v>1.9719</v>
       </c>
       <c r="G4" t="n">
         <v>0.1736</v>
@@ -766,13 +766,13 @@
         <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2388</v>
+        <v>0.1018</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.1586</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3484</v>
+        <v>0.2604</v>
       </c>
       <c r="V4" t="n">
         <v>1.8751</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. NDIAYE</t>
+          <t>N. SAGNIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3898</v>
+        <v>0.202</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1616</v>
+        <v>1.0679</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2282</v>
+        <v>-0.8658</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1607</v>
+        <v>-1.6128</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8101</v>
+        <v>-0.6952</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9707</v>
+        <v>-0.9177</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0965</v>
+        <v>-0.6168</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1447</v>
+        <v>-0.6952</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0482</v>
+        <v>0.0784</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2572</v>
+        <v>-0.996</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6654</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9225</v>
+        <v>-0.996</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.4829</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0619</v>
+        <v>0.2872</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6342</v>
+        <v>0.1957</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3538</v>
+        <v>0.7076</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0437</v>
+        <v>1.3975</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3975</v>
+        <v>-0.6899</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>S. NDIAYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1378</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.7744</v>
+        <v>-0.0528</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9122</v>
+        <v>0.1401</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6288</v>
+        <v>-0.1607</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.5415</v>
+        <v>0.8101</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9127999999999999</v>
+        <v>-0.9707</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.4696</v>
+        <v>0.0965</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.6272</v>
+        <v>0.1447</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1577</v>
+        <v>-0.0482</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8408</v>
+        <v>-0.2572</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0857</v>
+        <v>0.6654</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2449</v>
+        <v>-0.9225</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2893</v>
+        <v>0.2081</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2893</v>
+        <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5227</v>
+        <v>0.3937</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3049</v>
+        <v>-0.1524</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2179</v>
+        <v>0.5461</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0437</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. SCHUTTE</t>
+          <t>J. BLACK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0506</v>
+        <v>-0.4027</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4375</v>
+        <v>-0.1485</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4881</v>
+        <v>-0.2543</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7265</v>
+        <v>-1.1797</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4582</v>
+        <v>0.5438</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7316</v>
+        <v>-1.7235</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8696</v>
+        <v>0.7512</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7521</v>
+        <v>0.552</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1176</v>
+        <v>0.1992</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1431</v>
+        <v>-1.931</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7060999999999999</v>
+        <v>-0.0083</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8492</v>
+        <v>-1.9227</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.4568</v>
+        <v>0.2081</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6173</v>
+        <v>-0.0149</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2297</v>
+        <v>-0.4429</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3876</v>
+        <v>0.428</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9376</v>
+        <v>0.5838</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4599</v>
+        <v>0.5838</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.228</v>
+        <v>-0.6493</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1096</v>
+        <v>-2.0024</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8815</v>
+        <v>1.3531</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4237</v>
@@ -1078,13 +1078,13 @@
         <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2383</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2643</v>
+        <v>-0.1571</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5026</v>
+        <v>0.9741</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7076</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5599</v>
+        <v>-0.8829</v>
       </c>
       <c r="E9" t="n">
         <v>-2.6798</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1199</v>
+        <v>1.797</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8816</v>
@@ -1156,13 +1156,13 @@
         <v>2.0812</v>
       </c>
       <c r="S9" t="n">
-        <v>0.841</v>
+        <v>0.518</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0033</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.5213</v>
       </c>
       <c r="V9" t="n">
         <v>1.5213</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BLACK</t>
+          <t>K. SCHUTTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0853</v>
+        <v>-0.9372</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6842</v>
+        <v>-0.4197</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.401</v>
+        <v>-0.5174</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1797</v>
+        <v>0.7265</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5438</v>
+        <v>2.4582</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7235</v>
+        <v>-1.7316</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7512</v>
+        <v>1.8696</v>
       </c>
       <c r="K10" t="n">
-        <v>0.552</v>
+        <v>1.7521</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1992</v>
+        <v>0.1176</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.931</v>
+        <v>-1.1431</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0083</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.9227</v>
+        <v>-1.8492</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2081</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6974</v>
+        <v>0.7307</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9786</v>
+        <v>0.3725</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2812</v>
+        <v>0.3582</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5838</v>
+        <v>-0.9376</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5838</v>
+        <v>0.4599</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.5039</v>
+        <v>-7.6404</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.3116</v>
+        <v>-6.4187</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1923</v>
+        <v>-1.2216</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4525</v>
@@ -1312,13 +1312,13 @@
         <v>0.8325</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4867</v>
+        <v>0.3502</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0033</v>
+        <v>-0.1105</v>
       </c>
       <c r="U11" t="n">
-        <v>0.49</v>
+        <v>0.4606</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1675</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.768099999999999</v>
+        <v>-4.7681</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.656</v>
+        <v>-12.6561</v>
       </c>
       <c r="F12" t="n">
-        <v>7.888000000000002</v>
+        <v>7.888299999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-9.1431</v>
       </c>
       <c r="H12" t="n">
-        <v>2.429800000000001</v>
+        <v>2.4298</v>
       </c>
       <c r="I12" t="n">
         <v>-11.5727</v>
@@ -1372,10 +1372,10 @@
         <v>1.0409</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.470899999999999</v>
+        <v>-6.4709</v>
       </c>
       <c r="N12" t="n">
-        <v>6.142799999999999</v>
+        <v>6.142800000000001</v>
       </c>
       <c r="O12" t="n">
         <v>-12.6135</v>
@@ -1390,13 +1390,13 @@
         <v>14.5683</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1838</v>
+        <v>3.1837</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0117</v>
+        <v>-1.0118</v>
       </c>
       <c r="U12" t="n">
-        <v>4.1954</v>
+        <v>4.1953</v>
       </c>
       <c r="V12" t="n">
         <v>3.2726</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.193</v>
+        <v>4.4278</v>
       </c>
       <c r="E13" t="n">
         <v>2.238</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9549</v>
+        <v>2.1898</v>
       </c>
       <c r="G13" t="n">
         <v>2.6045</v>
@@ -1468,13 +1468,13 @@
         <v>2.7055</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9121</v>
+        <v>-0.6772</v>
       </c>
       <c r="T13" t="n">
         <v>-0.721</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1911</v>
+        <v>0.0438</v>
       </c>
       <c r="V13" t="n">
         <v>1.0437</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8744</v>
+        <v>3.215</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.2201</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5231</v>
+        <v>3.435</v>
       </c>
       <c r="G14" t="n">
         <v>1.9976</v>
@@ -1546,13 +1546,13 @@
         <v>2.0812</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.535</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9786</v>
+        <v>-0.55</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1031</v>
+        <v>0.0151</v>
       </c>
       <c r="V14" t="n">
         <v>0.9199000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5893</v>
+        <v>2.3926</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4802</v>
+        <v>0.6946</v>
       </c>
       <c r="F15" t="n">
-        <v>2.109</v>
+        <v>1.698</v>
       </c>
       <c r="G15" t="n">
         <v>1.096</v>
@@ -1624,13 +1624,13 @@
         <v>1.2487</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1207</v>
+        <v>-0.076</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5219</v>
+        <v>-0.3076</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6427</v>
+        <v>0.2317</v>
       </c>
       <c r="V15" t="n">
         <v>0.1238</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1564</v>
+        <v>1.8452</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5919</v>
+        <v>0.1633</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5645</v>
+        <v>1.6819</v>
       </c>
       <c r="G16" t="n">
         <v>4.5499</v>
@@ -1702,13 +1702,13 @@
         <v>3.1218</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0803</v>
+        <v>-0.3915</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1371</v>
+        <v>-0.5657</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0568</v>
+        <v>0.1743</v>
       </c>
       <c r="V16" t="n">
         <v>-2.1051</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4512</v>
+        <v>1.6567</v>
       </c>
       <c r="E17" t="n">
         <v>1.0354</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4158</v>
+        <v>0.6213</v>
       </c>
       <c r="G17" t="n">
         <v>1.917</v>
@@ -1780,13 +1780,13 @@
         <v>0.4162</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4221</v>
+        <v>-0.2166</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1305</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2916</v>
+        <v>-0.0861</v>
       </c>
       <c r="V17" t="n">
         <v>-0.4599</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. STEVANIC</t>
+          <t>T. TEIXEIRA DO VALE DIAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6847</v>
+        <v>-0.4488</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.259</v>
+        <v>-2.5698</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5744</v>
+        <v>2.1209</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0956</v>
+        <v>1.0351</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8466</v>
+        <v>-0.9872</v>
       </c>
       <c r="I18" t="n">
-        <v>0.249</v>
+        <v>2.0223</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1078</v>
+        <v>0.9373</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0384</v>
+        <v>-1.2605</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0694</v>
+        <v>2.1978</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9879</v>
+        <v>0.0978</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8082</v>
+        <v>0.2733</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1796</v>
+        <v>-0.1755</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4162</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6244</v>
+        <v>1.6649</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7803</v>
+        <v>-0.2571</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3262</v>
+        <v>-0.6153</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4541</v>
+        <v>0.3582</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5838</v>
+        <v>0.23</v>
       </c>
       <c r="W18" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-0.5838</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. TEIXEIRA DO VALE DIAS</t>
+          <t>V. STEVANIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8481</v>
+        <v>-0.5085</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9984</v>
+        <v>-1.259</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1503</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0351</v>
+        <v>1.0956</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9872</v>
+        <v>0.8466</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0223</v>
+        <v>0.249</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9373</v>
+        <v>0.1078</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2605</v>
+        <v>0.0384</v>
       </c>
       <c r="L19" t="n">
-        <v>2.1978</v>
+        <v>0.0694</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0978</v>
+        <v>0.9879</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2733</v>
+        <v>0.8082</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1755</v>
+        <v>0.1796</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.4568</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6563</v>
+        <v>-0.6041</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0439</v>
+        <v>-0.3262</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3876</v>
+        <v>-0.2779</v>
       </c>
       <c r="V19" t="n">
-        <v>0.23</v>
+        <v>-0.5838</v>
       </c>
       <c r="W19" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SERRANO ALVAREZ</t>
+          <t>S. KOCIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.743</v>
+        <v>-2.2544</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6478</v>
+        <v>-3.4798</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.09520000000000001</v>
+        <v>1.2254</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.0082</v>
+        <v>-3.6489</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.7037</v>
+        <v>-1.3237</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3045</v>
+        <v>-2.3252</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9672</v>
+        <v>-2.6812</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.1239</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1568</v>
+        <v>-2.0435</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0411</v>
+        <v>-0.9678</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5798</v>
+        <v>-0.6861</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4613</v>
+        <v>-0.2817</v>
       </c>
       <c r="P20" t="n">
+        <v>2.0812</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-0.2081</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-1.0406</v>
-      </c>
       <c r="R20" t="n">
-        <v>0.8325</v>
+        <v>2.2893</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1195</v>
+        <v>-0.4567</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1924</v>
+        <v>-0.5905</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9271</v>
+        <v>0.1338</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3538</v>
+        <v>-0.23</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8137</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. KOCIC</t>
+          <t>M. SERRANO ALVAREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3718</v>
+        <v>-2.4168</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4798</v>
+        <v>-1.9693</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1079</v>
+        <v>-0.4475</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.6489</v>
+        <v>-3.0082</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3237</v>
+        <v>-2.7037</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3252</v>
+        <v>-0.3045</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.6812</v>
+        <v>-1.9672</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-2.1239</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.0435</v>
+        <v>0.1568</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9678</v>
+        <v>-1.0411</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6861</v>
+        <v>-0.5798</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2817</v>
+        <v>-0.4613</v>
       </c>
       <c r="P21" t="n">
-        <v>2.0812</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2893</v>
+        <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5741000000000001</v>
+        <v>0.4458</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5905</v>
+        <v>-0.129</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0164</v>
+        <v>0.5748</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.23</v>
+        <v>0.3538</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.23</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8487</v>
+        <v>-3.1408</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2001</v>
+        <v>-2.5215</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6486</v>
+        <v>-0.6193</v>
       </c>
       <c r="G22" t="n">
         <v>1.5046</v>
@@ -2170,13 +2170,13 @@
         <v>1.6649</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1233</v>
+        <v>-0.4154</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0619</v>
+        <v>-0.2595</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1852</v>
+        <v>-0.1559</v>
       </c>
       <c r="V22" t="n">
         <v>-2.565</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.767999999999998</v>
+        <v>4.768000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.8883</v>
+        <v>-7.888199999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>12.6561</v>
+        <v>12.656</v>
       </c>
       <c r="G23" t="n">
-        <v>9.143200000000002</v>
+        <v>9.1432</v>
       </c>
       <c r="H23" t="n">
         <v>-2.4296</v>
@@ -2251,10 +2251,10 @@
         <v>-3.1838</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.195400000000001</v>
+        <v>-4.1953</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0117</v>
+        <v>1.0118</v>
       </c>
       <c r="V23" t="n">
         <v>-3.2726</v>
